--- a/Modelado/Input/Mayores Contables, Modelado Spreadsheet.xlsx
+++ b/Modelado/Input/Mayores Contables, Modelado Spreadsheet.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr fullPrecision="1" calcId="125725"/>
+  <definedNames/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29" count="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>Fecha</t>
   </si>
@@ -82,7 +83,7 @@
     <t>Cierre de Lote Nro.751</t>
   </si>
   <si>
-    <t>Cob Lote Nro. 143 s/Compr.305796</t>
+    <t>Cob. Lote Nro. 143 s/Compr.305796</t>
   </si>
   <si>
     <t>Cob. Lote Nro. 142 s/Compr.305718</t>
@@ -97,7 +98,7 @@
     <t>Cob. Lote Nro. 724 s/Compr.303983</t>
   </si>
   <si>
-    <t>Cierre de Lote Nor.148</t>
+    <t>Cierre de Lote Nro.148</t>
   </si>
   <si>
     <t>Totales:</t>
@@ -106,46 +107,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="64"/>
-        <bgColor indexed="65"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor indexed="64"/>
-        <bgColor indexed="65"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -157,66 +138,444 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyNumberFormat="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Hoja1LockedColumnStyle" xfId="20"/>
-    <cellStyle name="Hoja1UnLockedColumnStyle" xfId="21"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
+    <cellStyle name="Hoja1LockedColumnStyle" xfId="6"/>
+    <cellStyle name="Hoja1UnLockedColumnStyle" xfId="7"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr customHeight="true" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="32.41796875" customWidth="1"/>
-    <col min="4" max="6" width="11.41796875" customWidth="1"/>
+    <col min="3" max="3" width="32.4285714285714" customWidth="1"/>
+    <col min="4" max="6" width="11.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -236,7 +595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" ht="15">
       <c r="A2" s="2">
         <v>46023</v>
       </c>
@@ -254,7 +613,7 @@
         <v>19912.12</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="15">
       <c r="A3" s="2">
         <v>46026</v>
       </c>
@@ -272,7 +631,7 @@
         <v>20212.12</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="15">
       <c r="A4" s="2">
         <v>46027</v>
       </c>
@@ -290,7 +649,7 @@
         <v>20412.12</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="2">
         <v>46027</v>
       </c>
@@ -308,7 +667,7 @@
         <v>10487.12</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="15">
       <c r="A6" s="2">
         <v>46028</v>
       </c>
@@ -326,7 +685,7 @@
         <v>10687.12</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="15">
       <c r="A7" s="2">
         <v>46029</v>
       </c>
@@ -344,7 +703,7 @@
         <v>10387.12</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="15">
       <c r="A8" s="2">
         <v>46029</v>
       </c>
@@ -362,7 +721,7 @@
         <v>10187.12</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="15">
       <c r="A9" s="2">
         <v>46030</v>
       </c>
@@ -380,7 +739,7 @@
         <v>10487.12</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="15">
       <c r="A10" s="2">
         <v>46030</v>
       </c>
@@ -398,7 +757,7 @@
         <v>10287.12</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="15">
       <c r="A11" s="2">
         <v>46031</v>
       </c>
@@ -416,7 +775,7 @@
         <v>10407.12</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" ht="15">
       <c r="A12" s="2">
         <v>46031</v>
       </c>
@@ -434,7 +793,7 @@
         <v>8007.12</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="15">
       <c r="A13" s="2">
         <v>46031</v>
       </c>
@@ -452,7 +811,7 @@
         <v>5607.12</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" ht="15">
       <c r="A14" s="2">
         <v>46031</v>
       </c>
@@ -470,7 +829,7 @@
         <v>3207.12</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="15">
       <c r="A15" s="2">
         <v>46031</v>
       </c>
@@ -488,7 +847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" ht="15">
       <c r="A16" s="2">
         <v>46032</v>
       </c>
@@ -506,7 +865,7 @@
         <v>10217.12</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="15">
       <c r="A17" s="2">
         <v>46032</v>
       </c>
@@ -524,7 +883,7 @@
         <v>17142.12</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="15">
       <c r="A18" s="2">
         <v>46032</v>
       </c>
@@ -542,7 +901,7 @@
         <v>30992.12</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" ht="15">
       <c r="A19" s="2">
         <v>46032</v>
       </c>
@@ -560,7 +919,7 @@
         <v>31092.12</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" ht="15">
       <c r="A20" s="2">
         <v>46034</v>
       </c>
@@ -578,7 +937,7 @@
         <v>31392.12</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" ht="15">
       <c r="A21" s="2">
         <v>46035</v>
       </c>
@@ -596,7 +955,7 @@
         <v>17542.12</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="15">
       <c r="A22" s="2">
         <v>46035</v>
       </c>
@@ -614,7 +973,7 @@
         <v>10617.12</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" ht="15">
       <c r="A23" s="2">
         <v>46035</v>
       </c>
@@ -632,7 +991,7 @@
         <v>10317.12</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="15">
       <c r="A24" s="2">
         <v>46036</v>
       </c>
@@ -650,7 +1009,7 @@
         <v>10117.12</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" ht="15">
       <c r="A25" s="2">
         <v>46036</v>
       </c>
@@ -668,7 +1027,7 @@
         <v>9817.12</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" ht="15">
       <c r="A26" s="2">
         <v>46037</v>
       </c>
@@ -686,7 +1045,7 @@
         <v>15317.12</v>
       </c>
     </row>
-    <row r="27" spans="4:6">
+    <row r="27" spans="4:6" ht="15">
       <c r="D27" s="1" t="s">
         <v>28</v>
       </c>
@@ -699,7 +1058,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
-  <extLst/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>